--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,43 +796,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121205974</v>
+        <v>121206317</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593223</v>
+        <v>593352</v>
       </c>
       <c r="R3" t="n">
-        <v>6465193</v>
+        <v>6465282</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,47 +917,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206317</v>
+        <v>121206372</v>
       </c>
       <c r="B4" t="n">
-        <v>94844</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593352</v>
+        <v>593377</v>
       </c>
       <c r="R4" t="n">
         <v>6465282</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206372</v>
+        <v>121206173</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593377</v>
+        <v>593263</v>
       </c>
       <c r="R5" t="n">
-        <v>6465282</v>
+        <v>6465209</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
         <v>121206353</v>
       </c>
       <c r="B6" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206173</v>
+        <v>121205974</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,27 +1288,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593263</v>
+        <v>593223</v>
       </c>
       <c r="R7" t="n">
-        <v>6465209</v>
+        <v>6465193</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1392,7 @@
         <v>121225506</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>121226155</v>
       </c>
       <c r="B9" t="n">
-        <v>90074</v>
+        <v>90084</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>121225115</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206372</v>
+        <v>121206353</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,31 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593377</v>
+        <v>593358</v>
       </c>
       <c r="R4" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206173</v>
+        <v>121206372</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1070,7 +1074,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593263</v>
+        <v>593377</v>
       </c>
       <c r="R5" t="n">
-        <v>6465209</v>
+        <v>6465282</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1114,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206353</v>
+        <v>121205974</v>
       </c>
       <c r="B6" t="n">
-        <v>94854</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,35 +1167,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593358</v>
+        <v>593223</v>
       </c>
       <c r="R6" t="n">
-        <v>6465280</v>
+        <v>6465193</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121205974</v>
+        <v>121206173</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,27 +1288,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593223</v>
+        <v>593263</v>
       </c>
       <c r="R7" t="n">
-        <v>6465193</v>
+        <v>6465209</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225506</v>
+        <v>121225115</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593240</v>
+        <v>593304</v>
       </c>
       <c r="R8" t="n">
-        <v>6465194</v>
+        <v>6465345</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,6 +1473,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,17 +1497,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Jan Aronsson, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121226155</v>
+        <v>121225506</v>
       </c>
       <c r="B9" t="n">
-        <v>90084</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,48 +1516,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A 43507-2024 Svinsbo, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593440</v>
+        <v>593240</v>
       </c>
       <c r="R9" t="n">
-        <v>6465406</v>
+        <v>6465194</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,24 +1596,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1624,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121225115</v>
+        <v>121226155</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,46 +1626,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>5685</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 43507-2024 Svinsbo, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593304</v>
+        <v>593440</v>
       </c>
       <c r="R10" t="n">
-        <v>6465345</v>
+        <v>6465406</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1710,19 +1699,30 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I murken björk</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,47 +796,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206317</v>
+        <v>121206372</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593352</v>
+        <v>593377</v>
       </c>
       <c r="R3" t="n">
         <v>6465282</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206353</v>
+        <v>121206173</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,35 +925,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593358</v>
+        <v>593263</v>
       </c>
       <c r="R4" t="n">
-        <v>6465280</v>
+        <v>6465209</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,43 +1030,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206372</v>
+        <v>121206317</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>94866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593377</v>
+        <v>593352</v>
       </c>
       <c r="R5" t="n">
         <v>6465282</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1272,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206173</v>
+        <v>121206353</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>94866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,31 +1280,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593263</v>
+        <v>593358</v>
       </c>
       <c r="R7" t="n">
-        <v>6465209</v>
+        <v>6465280</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225115</v>
+        <v>121225506</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593304</v>
+        <v>593240</v>
       </c>
       <c r="R8" t="n">
-        <v>6465345</v>
+        <v>6465194</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,11 +1473,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,17 +1492,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121225506</v>
+        <v>121225115</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,21 +1515,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,7 +1537,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,13 +1547,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593240</v>
+        <v>593304</v>
       </c>
       <c r="R9" t="n">
-        <v>6465194</v>
+        <v>6465345</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,6 +1583,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,7 +1617,7 @@
         <v>121226155</v>
       </c>
       <c r="B10" t="n">
-        <v>90084</v>
+        <v>90092</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206372</v>
+        <v>121206173</v>
       </c>
       <c r="B3" t="n">
         <v>57367</v>
@@ -832,7 +832,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593377</v>
+        <v>593263</v>
       </c>
       <c r="R3" t="n">
-        <v>6465282</v>
+        <v>6465209</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206173</v>
+        <v>121205974</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,27 +929,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593263</v>
+        <v>593223</v>
       </c>
       <c r="R4" t="n">
-        <v>6465209</v>
+        <v>6465193</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,14 +1030,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206317</v>
+        <v>121206353</v>
       </c>
       <c r="B5" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593352</v>
+        <v>593358</v>
       </c>
       <c r="R5" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121205974</v>
+        <v>121206372</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,27 +1167,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593223</v>
+        <v>593377</v>
       </c>
       <c r="R6" t="n">
-        <v>6465193</v>
+        <v>6465282</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,14 +1268,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206353</v>
+        <v>121206317</v>
       </c>
       <c r="B7" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593358</v>
+        <v>593352</v>
       </c>
       <c r="R7" t="n">
-        <v>6465280</v>
+        <v>6465282</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1617,7 +1617,7 @@
         <v>121226155</v>
       </c>
       <c r="B10" t="n">
-        <v>90092</v>
+        <v>90093</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121206173</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205974</v>
+        <v>121206353</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>94870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593223</v>
+        <v>593358</v>
       </c>
       <c r="R4" t="n">
-        <v>6465193</v>
+        <v>6465280</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,14 +1034,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206353</v>
+        <v>121206317</v>
       </c>
       <c r="B5" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593358</v>
+        <v>593352</v>
       </c>
       <c r="R5" t="n">
-        <v>6465280</v>
+        <v>6465282</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1158,7 @@
         <v>121206372</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1268,47 +1272,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206317</v>
+        <v>121205974</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593352</v>
+        <v>593223</v>
       </c>
       <c r="R7" t="n">
-        <v>6465282</v>
+        <v>6465193</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225506</v>
+        <v>121226155</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>90096</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,49 +1401,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 43507-2024 Svinsbo, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593240</v>
+        <v>593440</v>
       </c>
       <c r="R8" t="n">
-        <v>6465194</v>
+        <v>6465406</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,8 +1480,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1502,7 +1517,7 @@
         <v>121225115</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121226155</v>
+        <v>121225506</v>
       </c>
       <c r="B10" t="n">
-        <v>90093</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,48 +1641,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A 43507-2024 Svinsbo, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593440</v>
+        <v>593240</v>
       </c>
       <c r="R10" t="n">
-        <v>6465406</v>
+        <v>6465194</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,24 +1721,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -913,14 +913,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206353</v>
+        <v>121206317</v>
       </c>
       <c r="B4" t="n">
         <v>94870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593358</v>
+        <v>593352</v>
       </c>
       <c r="R4" t="n">
-        <v>6465280</v>
+        <v>6465282</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,14 +1034,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206317</v>
+        <v>121206353</v>
       </c>
       <c r="B5" t="n">
         <v>94870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593352</v>
+        <v>593358</v>
       </c>
       <c r="R5" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206372</v>
+        <v>121205974</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,27 +1171,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593377</v>
+        <v>593223</v>
       </c>
       <c r="R6" t="n">
-        <v>6465282</v>
+        <v>6465193</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121205974</v>
+        <v>121206372</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,27 +1288,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593223</v>
+        <v>593377</v>
       </c>
       <c r="R7" t="n">
-        <v>6465193</v>
+        <v>6465282</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206173</v>
+        <v>121206372</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593263</v>
+        <v>593377</v>
       </c>
       <c r="R3" t="n">
-        <v>6465209</v>
+        <v>6465282</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,14 +913,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206317</v>
+        <v>121206353</v>
       </c>
       <c r="B4" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593352</v>
+        <v>593358</v>
       </c>
       <c r="R4" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206353</v>
+        <v>121205974</v>
       </c>
       <c r="B5" t="n">
-        <v>94870</v>
+        <v>57508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,35 +1046,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593358</v>
+        <v>593223</v>
       </c>
       <c r="R5" t="n">
-        <v>6465280</v>
+        <v>6465193</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121205974</v>
+        <v>121206173</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,27 +1167,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593223</v>
+        <v>593263</v>
       </c>
       <c r="R6" t="n">
-        <v>6465193</v>
+        <v>6465209</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,43 +1268,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206372</v>
+        <v>121206317</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>94876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593377</v>
+        <v>593352</v>
       </c>
       <c r="R7" t="n">
         <v>6465282</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1392,7 @@
         <v>121226155</v>
       </c>
       <c r="B8" t="n">
-        <v>90096</v>
+        <v>90102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121225115</v>
+        <v>121225506</v>
       </c>
       <c r="B9" t="n">
-        <v>57360</v>
+        <v>57508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593304</v>
+        <v>593240</v>
       </c>
       <c r="R9" t="n">
-        <v>6465345</v>
+        <v>6465194</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,11 +1598,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121225506</v>
+        <v>121225115</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>57361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1640,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,7 +1662,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1677,13 +1672,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593240</v>
+        <v>593304</v>
       </c>
       <c r="R10" t="n">
-        <v>6465194</v>
+        <v>6465345</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,6 +1708,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206372</v>
+        <v>121206353</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593377</v>
+        <v>593358</v>
       </c>
       <c r="R3" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206353</v>
+        <v>121206372</v>
       </c>
       <c r="B4" t="n">
-        <v>94876</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593358</v>
+        <v>593377</v>
       </c>
       <c r="R4" t="n">
-        <v>6465280</v>
+        <v>6465282</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1037,7 @@
         <v>121205974</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1151,43 +1151,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206173</v>
+        <v>121206317</v>
       </c>
       <c r="B6" t="n">
-        <v>57371</v>
+        <v>94877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593263</v>
+        <v>593352</v>
       </c>
       <c r="R6" t="n">
-        <v>6465209</v>
+        <v>6465282</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,47 +1272,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206317</v>
+        <v>121206173</v>
       </c>
       <c r="B7" t="n">
-        <v>94876</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593352</v>
+        <v>593263</v>
       </c>
       <c r="R7" t="n">
-        <v>6465282</v>
+        <v>6465209</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121226155</v>
+        <v>121225506</v>
       </c>
       <c r="B8" t="n">
-        <v>90102</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,48 +1401,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A 43507-2024 Svinsbo, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593440</v>
+        <v>593240</v>
       </c>
       <c r="R8" t="n">
-        <v>6465406</v>
+        <v>6465194</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,24 +1481,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1514,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121225506</v>
+        <v>121226155</v>
       </c>
       <c r="B9" t="n">
-        <v>57508</v>
+        <v>90103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,49 +1511,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 43507-2024 Svinsbo, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593240</v>
+        <v>593440</v>
       </c>
       <c r="R9" t="n">
-        <v>6465194</v>
+        <v>6465406</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,8 +1590,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1627,7 +1627,7 @@
         <v>121225115</v>
       </c>
       <c r="B10" t="n">
-        <v>57361</v>
+        <v>57362</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -796,14 +796,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206353</v>
+        <v>121206317</v>
       </c>
       <c r="B3" t="n">
         <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593358</v>
+        <v>593352</v>
       </c>
       <c r="R3" t="n">
-        <v>6465280</v>
+        <v>6465282</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206372</v>
+        <v>121206353</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>94877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,31 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593377</v>
+        <v>593358</v>
       </c>
       <c r="R4" t="n">
-        <v>6465282</v>
+        <v>6465280</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1151,47 +1155,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206317</v>
+        <v>121206173</v>
       </c>
       <c r="B6" t="n">
-        <v>94877</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593352</v>
+        <v>593263</v>
       </c>
       <c r="R6" t="n">
-        <v>6465282</v>
+        <v>6465209</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206173</v>
+        <v>121206372</v>
       </c>
       <c r="B7" t="n">
         <v>57372</v>
@@ -1308,7 +1308,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593263</v>
+        <v>593377</v>
       </c>
       <c r="R7" t="n">
-        <v>6465209</v>
+        <v>6465282</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225506</v>
+        <v>121226155</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>90103</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,49 +1401,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 43507-2024 Svinsbo, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593240</v>
+        <v>593440</v>
       </c>
       <c r="R8" t="n">
-        <v>6465194</v>
+        <v>6465406</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,8 +1480,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1499,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121226155</v>
+        <v>121225115</v>
       </c>
       <c r="B9" t="n">
-        <v>90103</v>
+        <v>57362</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,45 +1526,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A 43507-2024 Svinsbo, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593440</v>
+        <v>593304</v>
       </c>
       <c r="R9" t="n">
-        <v>6465406</v>
+        <v>6465345</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,30 +1600,19 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I murken björk</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1624,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121225115</v>
+        <v>121225506</v>
       </c>
       <c r="B10" t="n">
-        <v>57362</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,21 +1645,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1662,7 +1667,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1672,13 +1677,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593304</v>
+        <v>593240</v>
       </c>
       <c r="R10" t="n">
-        <v>6465345</v>
+        <v>6465194</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,11 +1713,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I murken björk</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -1517,11 +1517,11 @@
         <v>121225115</v>
       </c>
       <c r="B9" t="n">
-        <v>57362</v>
+        <v>57484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/artfynd/A 43507-2024 artfynd.xlsx
+++ b/artfynd/A 43507-2024 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>121225115</v>
       </c>
       <c r="B9" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
